--- a/final_result/etf/momentum_us_rs_etfs.xlsx
+++ b/final_result/etf/momentum_us_rs_etfs.xlsx
@@ -489,43 +489,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DXYZ</t>
+          <t>WGMI</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>59.33</v>
+        <v>65.86</v>
       </c>
       <c r="D2" t="n">
-        <v>50.99</v>
+        <v>66.45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>30.3</v>
+        <v>-6.9</v>
       </c>
       <c r="G2" t="n">
-        <v>31.8</v>
+        <v>6.3</v>
       </c>
       <c r="H2" t="n">
-        <v>101.1</v>
+        <v>13.5</v>
       </c>
       <c r="I2" t="n">
-        <v>111.1</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>31</v>
+        <v>-4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>30.3</v>
+        <v>7.3</v>
       </c>
       <c r="L2" t="n">
-        <v>96.3</v>
+        <v>13.4</v>
       </c>
       <c r="M2" t="n">
-        <v>103.3</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="3">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>523.1</v>
+        <v>571.23</v>
       </c>
       <c r="D3" t="n">
-        <v>510.4</v>
+        <v>571.21</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -549,28 +549,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H3" t="n">
-        <v>18.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>45.6</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7</v>
+        <v>2.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>13.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>37.8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -579,43 +579,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EWY</t>
+          <t>SOXQ</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>186.35</v>
+        <v>101.47</v>
       </c>
       <c r="D4" t="n">
-        <v>180.42</v>
+        <v>101.71</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-2.2</v>
+        <v>-0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>23.7</v>
+        <v>9.5</v>
       </c>
       <c r="I4" t="n">
-        <v>31.3</v>
+        <v>65.2</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.5</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>18.9</v>
+        <v>9.4</v>
       </c>
       <c r="M4" t="n">
-        <v>23.5</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="5">
@@ -624,43 +624,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>CHPS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>178.22</v>
+        <v>90.47</v>
       </c>
       <c r="D5" t="n">
-        <v>175.09</v>
+        <v>91.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-0.7</v>
+        <v>-2</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="H5" t="n">
-        <v>14.4</v>
+        <v>7.5</v>
       </c>
       <c r="I5" t="n">
-        <v>26.7</v>
+        <v>65.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="L5" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>18.8</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="6">
@@ -669,43 +669,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>ARTY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.26</v>
+        <v>73.94</v>
       </c>
       <c r="D6" t="n">
-        <v>21.56</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>-5.3</v>
       </c>
       <c r="G6" t="n">
         <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>10.6</v>
+        <v>8.1</v>
       </c>
       <c r="I6" t="n">
-        <v>17.7</v>
+        <v>50.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>-2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="L6" t="n">
-        <v>5.7</v>
+        <v>8.1</v>
       </c>
       <c r="M6" t="n">
-        <v>9.9</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="7">
@@ -714,43 +714,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>FTXL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>65.05</v>
+        <v>258</v>
       </c>
       <c r="D7" t="n">
-        <v>62.91</v>
+        <v>259.53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="G7" t="n">
-        <v>8.9</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="I7" t="n">
-        <v>8.800000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -759,14 +759,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>CHAT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>141.22</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>144.35</v>
+        <v>95.92</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -774,28 +774,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-1.2</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="I8" t="n">
-        <v>74.7</v>
+        <v>46.4</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6</v>
+        <v>-5.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>66.8</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="9">
@@ -804,43 +804,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MTUM</t>
+          <t>WTAI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>302.06</v>
+        <v>43.3</v>
       </c>
       <c r="D9" t="n">
-        <v>298.46</v>
+        <v>43.97</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-1.7</v>
+        <v>-5.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
-        <v>18.7</v>
+        <v>47.7</v>
       </c>
       <c r="J9" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
       <c r="M9" t="n">
-        <v>10.8</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="10">
@@ -849,43 +849,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XNTK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>714.86</v>
+        <v>365.48</v>
       </c>
       <c r="D10" t="n">
-        <v>707.2</v>
+        <v>367.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-0.7</v>
+        <v>-3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="n">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I10" t="n">
-        <v>17.6</v>
+        <v>35.2</v>
       </c>
       <c r="J10" t="n">
-        <v>-0</v>
+        <v>-0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="M10" t="n">
-        <v>9.699999999999999</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="11">
@@ -894,43 +894,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EWT</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>94.7</v>
+        <v>597.78</v>
       </c>
       <c r="D11" t="n">
-        <v>92.77</v>
+        <v>600.86</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-0.8</v>
+        <v>-1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>12.4</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
-        <v>27.3</v>
+        <v>51.6</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2</v>
+        <v>0.9</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="M11" t="n">
-        <v>19.5</v>
+        <v>42.6</v>
       </c>
     </row>
   </sheetData>
